--- a/종이판지_수출입통계_update.xlsx
+++ b/종이판지_수출입통계_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kita\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB1BF99-57E0-498D-8890-E9181074AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4C6D56-1771-41C9-8321-95C9B0CA5306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD15722-B361-457C-8C7B-F124E2176285}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD15722-B361-457C-8C7B-F124E2176285}"/>
   </bookViews>
   <sheets>
     <sheet name="종이판지" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2905" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="37">
   <si>
     <t>연도</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -618,7 +618,7 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:E1335"/>
+  <dimension ref="A1:E1393"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -23322,6 +23322,992 @@
         <v>134795.33799999999</v>
       </c>
     </row>
+    <row r="1336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1336" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1336" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1336" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1336" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1336" s="5">
+        <v>6200.9470000000001</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1337" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1337" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1337" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1337" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1337" s="5">
+        <v>8976.6620000000003</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1338" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1338" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1338" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1338" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1338" s="5">
+        <v>233.32900000000001</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1339" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1339" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1339" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1339" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1339" s="5">
+        <v>58510.002</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1340" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1340" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1340" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1340" s="5">
+        <v>1799.4090000000001</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1341" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1341" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1341" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1341" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1341" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1342" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1342" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1342" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1342" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1342" s="5">
+        <v>5255.6090000000004</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1343" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1343" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1343" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1343" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1343" s="5">
+        <v>100.279</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1344" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1344" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1344" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1344" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1344" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1345" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1345" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1345" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1345" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1345" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1346" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1346" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1346" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1346" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1346" s="5">
+        <v>67.384</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1347" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1347" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1347" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1347" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1347" s="5">
+        <v>276.37400000000002</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1348" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1348" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1348" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1348" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1348" s="5">
+        <v>1718.58</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1349" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1349" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1349" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1349" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1349" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1350" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1350" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1350" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1350" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1350" s="5">
+        <v>48802.167999999998</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1351" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1351" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1351" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1351" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1351" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1352" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1352" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1352" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1352" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1352" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1353" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1353" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1353" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1353" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1353" s="5">
+        <v>114.065</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1354" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1354" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1354" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1354" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1354" s="5">
+        <v>6030.8969999999999</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1355" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1355" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1355" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1355" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1355" s="5">
+        <v>33547.93</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1356" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1356" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1356" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1356" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1356" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1357" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1357" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1357" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1357" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1357" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1358" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1358" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1358" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1358" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1358" s="5">
+        <v>3264.0410000000002</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1359" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1359" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1359" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1359" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1359" s="5">
+        <v>4084.8879999999999</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1360" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1360" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1360" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1360" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1360" s="5">
+        <v>141.93199999999999</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1361" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1361" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1361" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1361" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1361" s="5">
+        <v>20.157</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1362" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1362" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1362" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1362" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1362" s="5">
+        <v>83.016999999999996</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1363" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1363" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1363" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1363" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1363" s="7">
+        <v>201197.88800000001</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1364" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1364" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1364" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1364" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1364" s="7">
+        <v>217155.57399999999</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1365" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1365" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1365" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1365" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1365" s="5">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1366" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1366" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1366" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1366" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1366" s="5">
+        <v>2730.57</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1367" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1367" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1367" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1367" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1367" s="5">
+        <v>145.029</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1368" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1368" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1368" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1368" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1368" s="5">
+        <v>2985.5160000000001</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1369" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1369" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1369" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1369" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1369" s="5">
+        <v>161.376</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1370" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1370" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1370" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1370" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1370" s="5">
+        <v>568.327</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1371" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1371" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1371" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1371" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1371" s="5">
+        <v>488.89600000000002</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1372" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1372" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1372" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1372" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1372" s="5">
+        <v>7656.5690000000004</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1373" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1373" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1373" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1373" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1373" s="5">
+        <v>62.798000000000002</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1374" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1374" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1374" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1374" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1374" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1375" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1375" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1375" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1375" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1375" s="5">
+        <v>626.36</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1376" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1376" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1376" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1376" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1376" s="5">
+        <v>16635.513999999999</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1377" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1377" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1377" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1377" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1377" s="5">
+        <v>3578.64</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1378" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1378" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1378" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1378" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1378" s="5">
+        <v>1245.3630000000001</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1379" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1379" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1379" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1379" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1379" s="8">
+        <v>3822.4949999999999</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1380" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1380" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1380" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1380" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1380" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1381" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1381" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1381" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1381" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1381" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1382" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1382" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1382" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1382" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1382" s="5">
+        <v>1617.3869999999999</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1383" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1383" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1383" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1383" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1383" s="5">
+        <v>17141.627</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1384" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1384" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1384" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1384" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1384" s="5">
+        <v>4702.8639999999996</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1385" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1385" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1385" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1385" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1385" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1386" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1386" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1386" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1386" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1386" s="5">
+        <v>2218.9</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1387" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1387" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1387" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1387" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1387" s="5">
+        <v>6124.8689999999997</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1388" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1388" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1388" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1388" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1388" s="5">
+        <v>1352.6130000000001</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1389" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1389" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1389" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1389" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1389" s="5">
+        <v>202.14400000000001</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1390" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1390" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1390" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1390" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1390" s="5">
+        <v>174.62799999999999</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1391" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1391" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1391" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1391" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1391" s="5">
+        <v>4045.2</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1392" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1392" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1392" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1392" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1392" s="9">
+        <v>100296.626</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1393" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1393" s="1">
+        <v>8</v>
+      </c>
+      <c r="C1393" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1393" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1393" s="9">
+        <v>121166.72500000001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/종이판지_수출입통계_update.xlsx
+++ b/종이판지_수출입통계_update.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kita\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4C6D56-1771-41C9-8321-95C9B0CA5306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8653D4CB-7827-4416-9632-4985FF7DD41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD15722-B361-457C-8C7B-F124E2176285}"/>
   </bookViews>
   <sheets>
     <sheet name="종이판지" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">종이판지!$A$1:$E$1393</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -15142,7 +15145,7 @@
         <v>17</v>
       </c>
       <c r="E854" s="5">
-        <v>10</v>
+        <v>10493.578</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.3">
@@ -24309,6 +24312,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1393" xr:uid="{BCAE69C0-E9AF-4C84-BDB1-27E3DC4394F7}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/종이판지_수출입통계_update.xlsx
+++ b/종이판지_수출입통계_update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kita\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8653D4CB-7827-4416-9632-4985FF7DD41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884FE7CB-EF8F-4EF5-9177-4F21BA31DA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD15722-B361-457C-8C7B-F124E2176285}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{9AD15722-B361-457C-8C7B-F124E2176285}"/>
   </bookViews>
   <sheets>
     <sheet name="종이판지" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="37">
   <si>
     <t>연도</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -621,7 +621,7 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:E1393"/>
+  <dimension ref="A1:E1451"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -24311,6 +24311,992 @@
         <v>121166.72500000001</v>
       </c>
     </row>
+    <row r="1394" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1394" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1394" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1394" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1394" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1394" s="5">
+        <v>8468.5409999999993</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1395" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1395" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1395" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1395" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1395" s="5">
+        <v>6834.3130000000001</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1396" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1396" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1396" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1396" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1396" s="5">
+        <v>110.057</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1397" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1397" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1397" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1397" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1397" s="5">
+        <v>55850.313000000002</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1398" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1398" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1398" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1398" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1398" s="5">
+        <v>1882.5820000000001</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1399" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1399" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1399" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1399" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1399" s="5">
+        <v>75.238</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1400" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1400" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1400" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1400" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1400" s="5">
+        <v>4600.3029999999999</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1401" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1401" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1401" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1401" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1401" s="5">
+        <v>96.965000000000003</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1402" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1402" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1402" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1402" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1402" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1403" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1403" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1403" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1403" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1403" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1404" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1404" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1404" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1404" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1404" s="5">
+        <v>45.594999999999999</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1405" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1405" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1405" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1405" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1405" s="5">
+        <v>283.709</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1406" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1406" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1406" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1406" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1406" s="5">
+        <v>1628.867</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1407" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1407" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1407" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1407" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1407" s="5">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1408" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1408" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1408" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1408" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1408" s="5">
+        <v>51541.762999999999</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1409" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1409" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1409" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1409" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1409" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1410" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1410" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1410" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1410" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1410" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1411" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1411" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1411" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1411" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1411" s="5">
+        <v>225.25200000000001</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1412" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1412" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1412" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1412" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1412" s="5">
+        <v>6457.4089999999997</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1413" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1413" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1413" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1413" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1413" s="5">
+        <v>41680.495000000003</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1414" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1414" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1414" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1414" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1414" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1415" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1415" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1415" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1415" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1415" s="5">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1416" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1416" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1416" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1416" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1416" s="5">
+        <v>3273.39</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1417" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1417" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1417" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1417" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1417" s="5">
+        <v>4022.0219999999999</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1418" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1418" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1418" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1418" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1418" s="5">
+        <v>199.34</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1419" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1419" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1419" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1419" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1419" s="5">
+        <v>20.350000000000001</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1420" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1420" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1420" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1420" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1420" s="5">
+        <v>161.65</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1421" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1421" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1421" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1421" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1421" s="7">
+        <v>210493.31700000001</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1422" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1422" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1422" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1422" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1422" s="7">
+        <v>226074.97</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1423" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1423" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1423" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1423" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1423" s="5">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1424" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1424" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1424" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1424" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1424" s="5">
+        <v>2992.538</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1425" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1425" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1425" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1425" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1425" s="5">
+        <v>155.792</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1426" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1426" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1426" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1426" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1426" s="5">
+        <v>4853.1260000000002</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1427" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1427" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1427" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1427" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1427" s="5">
+        <v>202.08799999999999</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1428" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1428" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1428" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1428" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1428" s="5">
+        <v>1112.4269999999999</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1429" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1429" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1429" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1429" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1429" s="5">
+        <v>378.96100000000001</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1430" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1430" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1430" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1430" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1430" s="5">
+        <v>8374.143</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1431" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1431" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1431" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1431" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1431" s="5">
+        <v>241.63800000000001</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1432" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1432" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1432" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1432" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1432" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1433" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1433" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1433" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1433" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1433" s="5">
+        <v>801.58699999999999</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1434" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1434" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1434" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1434" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1434" s="5">
+        <v>18039.982</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1435" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1435" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1435" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1435" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1435" s="5">
+        <v>5395.5479999999998</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1436" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1436" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1436" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1436" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1436" s="5">
+        <v>1007.961</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1437" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1437" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1437" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1437" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1437" s="8">
+        <v>5456.5060000000003</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1438" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1438" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1438" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1438" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1438" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1439" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1439" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1439" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1439" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1439" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1440" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1440" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1440" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1440" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1440" s="5">
+        <v>2501.0909999999999</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1441" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1441" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1441" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1441" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1441" s="5">
+        <v>15321.136</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1442" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1442" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1442" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1442" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1442" s="5">
+        <v>1379.912</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1443" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1443" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1443" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1443" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1443" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1444" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1444" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1444" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1444" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1444" s="5">
+        <v>1744.26</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1445" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1445" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1445" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1445" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1445" s="5">
+        <v>7231.5330000000004</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1446" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1446" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1446" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1446" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1446" s="5">
+        <v>1444.877</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1447" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1447" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1447" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1447" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1447" s="5">
+        <v>148.72399999999999</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1448" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1448" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1448" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1448" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1448" s="5">
+        <v>461.16</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1449" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1449" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1449" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1449" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1449" s="5">
+        <v>4405.4470000000001</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1450" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1450" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1450" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1450" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1450" s="9">
+        <v>105837.37699999999</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1451" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B1451" s="1">
+        <v>9</v>
+      </c>
+      <c r="C1451" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1451" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1451" s="9">
+        <v>129155.966</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1393" xr:uid="{BCAE69C0-E9AF-4C84-BDB1-27E3DC4394F7}"/>
   <phoneticPr fontId="2" type="noConversion"/>
